--- a/lcoe/liquid_fuels/bio_liquid_fuels_lcoe/LCOE_BIOLF_TEMPLATE.xlsx
+++ b/lcoe/liquid_fuels/bio_liquid_fuels_lcoe/LCOE_BIOLF_TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abbie/Desktop/Dolphyn_to_Macro/Dolphyn vs. Macro/Python Codes/lcoe/liquid_fuels/bio_liquid_fuels_lcoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C1CB96-8F05-9D41-BE08-97A0E8E82DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2334D9DE-A955-2447-A8EB-57BC2FF766C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="500" windowWidth="38400" windowHeight="23500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29400" yWindow="500" windowWidth="38400" windowHeight="22620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lc_detailed" sheetId="1" r:id="rId1"/>
@@ -57246,7 +57246,7 @@
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>31</v>
